--- a/normal_enemy_names_for_12_waves.xlsx
+++ b/normal_enemy_names_for_12_waves.xlsx
@@ -1,37 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wh\Documents\arc-nice\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43922CC7-7F0E-4206-89B0-2492F8D13AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Enemies" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>波次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场间时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场上敌人数量上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒刷怪量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>基础原石虫</t>
   </si>
   <si>
+    <t>硬壳原石虫</t>
+  </si>
+  <si>
+    <t>自爆原石虫</t>
+  </si>
+  <si>
+    <t>紫晶自爆原石虫</t>
+  </si>
+  <si>
+    <t>火焰弹原石虫</t>
+  </si>
+  <si>
     <t>迅捷原石虫</t>
-  </si>
-  <si>
-    <t>硬壳原石虫</t>
-  </si>
-  <si>
-    <t>自爆原石虫</t>
-  </si>
-  <si>
-    <t>紫晶自爆原石虫</t>
-  </si>
-  <si>
-    <t>火焰弹原石虫</t>
   </si>
   <si>
     <t>翠壳原石虫</t>
@@ -66,12 +93,337 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="9.75" customWidth="1"/>
+    <col min="6" max="6" width="11.25" customWidth="1"/>
+    <col min="7" max="7" width="11.75" customWidth="1"/>
+    <col min="8" max="8" width="12.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -88,19 +440,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
@@ -120,8 +472,465 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>160</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2">
+        <v>40</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>240</v>
+      </c>
+      <c r="F3">
+        <v>70</v>
+      </c>
+      <c r="G3">
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>110</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>240</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>110</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>120</v>
+      </c>
+      <c r="F5">
+        <v>120</v>
+      </c>
+      <c r="H5">
+        <v>150</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>130</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>120</v>
+      </c>
+      <c r="F6">
+        <v>120</v>
+      </c>
+      <c r="G6">
+        <v>40</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>130</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>120</v>
+      </c>
+      <c r="F7">
+        <v>120</v>
+      </c>
+      <c r="H7">
+        <v>30</v>
+      </c>
+      <c r="I7">
+        <v>90</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>150</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>120</v>
+      </c>
+      <c r="F8">
+        <v>120</v>
+      </c>
+      <c r="I8">
+        <v>40</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>80</v>
+      </c>
+      <c r="N8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <v>150</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="G9">
+        <v>120</v>
+      </c>
+      <c r="I9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>180</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>120</v>
+      </c>
+      <c r="I10">
+        <v>30</v>
+      </c>
+      <c r="K10">
+        <v>20</v>
+      </c>
+      <c r="M10">
+        <v>20</v>
+      </c>
+      <c r="N10">
+        <v>20</v>
+      </c>
+      <c r="O10">
+        <v>20</v>
+      </c>
+      <c r="P10">
+        <v>60</v>
+      </c>
+      <c r="S10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>180</v>
+      </c>
+      <c r="D11">
+        <v>14</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>120</v>
+      </c>
+      <c r="I11">
+        <v>60</v>
+      </c>
+      <c r="L11">
+        <v>50</v>
+      </c>
+      <c r="M11">
+        <v>20</v>
+      </c>
+      <c r="N11">
+        <v>20</v>
+      </c>
+      <c r="O11">
+        <v>20</v>
+      </c>
+      <c r="P11">
+        <v>80</v>
+      </c>
+      <c r="R11">
+        <v>10</v>
+      </c>
+      <c r="S11">
+        <v>15</v>
+      </c>
+      <c r="T11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>30</v>
+      </c>
+      <c r="C12">
+        <v>200</v>
+      </c>
+      <c r="D12">
+        <v>16</v>
+      </c>
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12">
+        <v>50</v>
+      </c>
+      <c r="I12">
+        <v>50</v>
+      </c>
+      <c r="L12">
+        <v>50</v>
+      </c>
+      <c r="M12">
+        <v>20</v>
+      </c>
+      <c r="N12">
+        <v>10</v>
+      </c>
+      <c r="O12">
+        <v>60</v>
+      </c>
+      <c r="P12">
+        <v>20</v>
+      </c>
+      <c r="Q12">
+        <v>50</v>
+      </c>
+      <c r="R12">
+        <v>20</v>
+      </c>
+      <c r="S12">
+        <v>30</v>
+      </c>
+      <c r="T12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>30</v>
+      </c>
+      <c r="C13">
+        <v>200</v>
+      </c>
+      <c r="D13">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>50</v>
+      </c>
+      <c r="H13">
+        <v>30</v>
+      </c>
+      <c r="I13">
+        <v>50</v>
+      </c>
+      <c r="L13">
+        <v>50</v>
+      </c>
+      <c r="M13">
+        <v>20</v>
+      </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>80</v>
+      </c>
+      <c r="P13">
+        <v>20</v>
+      </c>
+      <c r="Q13">
+        <v>50</v>
+      </c>
+      <c r="R13">
+        <v>20</v>
+      </c>
+      <c r="S13">
+        <v>60</v>
+      </c>
+      <c r="T13">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>